--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:24</t>
+    <t xml:space="preserve">2026-09-09 23:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:20</t>
+    <t xml:space="preserve">2026-09-17 14:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:15</t>
+    <t xml:space="preserve">2026-09-23 12:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:44</t>
+    <t xml:space="preserve">2026-10-02 14:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_biobio.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">San Rosendo</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Coronel</t>
@@ -117,7 +117,7 @@
     <t xml:space="preserve">Cañete</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Lota</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:54</t>
+    <t xml:space="preserve">2026-10-04 09:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:15</t>
+    <t xml:space="preserve">2026-10-05 11:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
